--- a/Assets/Resources/story/2.xlsx
+++ b/Assets/Resources/story/2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\Resources\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4CF447-B7A4-4DD2-B632-2BDA912C49F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CFB63D-8D5F-4C24-A010-25E5D07E2D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2090" yWindow="3520" windowWidth="19200" windowHeight="9390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8510" yWindow="2730" windowWidth="19200" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -96,11 +96,19 @@
     <t>再见了。</t>
   </si>
   <si>
-    <t>End of story</t>
+    <t>邮件吗了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>邮件吗了</t>
+    <t>choice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,6 +436,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294B3738-0B50-4E27-88C2-74BD7B9AAF95}">
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -472,13 +483,13 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -594,7 +605,19 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/story/2.xlsx
+++ b/Assets/Resources/story/2.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\Resources\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CFB63D-8D5F-4C24-A010-25E5D07E2D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0829E166-ECEC-4F4C-B448-B45703951346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8510" yWindow="2730" windowWidth="19200" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7590" yWindow="1990" windowWidth="20000" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -109,6 +109,22 @@
   </si>
   <si>
     <t>choice2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastBGlmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastBGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,13 +450,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294B3738-0B50-4E27-88C2-74BD7B9AAF95}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,8 +493,20 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -504,7 +532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -529,8 +557,24 @@
       <c r="L3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <f>IF(E2&lt;&gt;"",E2,M2)</f>
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <f>IF(F2&lt;&gt;"",F2,N2)</f>
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <f>IF(H2&lt;&gt;"",H2,O2)</f>
+        <v>-500</v>
+      </c>
+      <c r="P3">
+        <f>IF(K2&lt;&gt;"",K2,P2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -540,8 +584,24 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4">
+        <f t="shared" ref="M4:N8" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f t="shared" ref="O4:O8" si="1">IF(H3&lt;&gt;"",H3,O3)</f>
+        <v>-400</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P8" si="2">IF(K3&lt;&gt;"",K3,P3)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -557,8 +617,24 @@
       <c r="K5">
         <v>700</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="1"/>
+        <v>-400</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -568,8 +644,24 @@
       <c r="C6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>-400</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -585,8 +677,24 @@
       <c r="K7">
         <v>800</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>-400</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -602,8 +710,24 @@
       <c r="H8">
         <v>-500</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>-400</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
